--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104561_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104561_W12.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1512</v>
+        <v>5.7002</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858</v>
+        <v>3.2436</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2932</v>
+        <v>2.4566</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6188</v>
+        <v>4.6097</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0014</v>
+        <v>2.0018</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6175</v>
+        <v>2.6079</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5191</v>
+        <v>3.4731</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9253</v>
+        <v>1.9026</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5938</v>
+        <v>1.5705</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0998</v>
+        <v>1.1366</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0761</v>
+        <v>0.0993</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6284</v>
+        <v>-0.0673</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.234</v>
+        <v>0.2062</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3944</v>
+        <v>-0.2734</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.223</v>
+        <v>4.1504</v>
       </c>
       <c r="E3" t="n">
-        <v>1.943</v>
+        <v>3.0614</v>
       </c>
       <c r="F3" t="n">
-        <v>1.28</v>
+        <v>1.0891</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8852</v>
+        <v>2.8971</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5972</v>
+        <v>2.6019</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2879</v>
+        <v>0.2953</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4582</v>
+        <v>1.445</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0953</v>
+        <v>2.0857</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4269</v>
+        <v>1.4522</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O3" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5695</v>
+        <v>0.3428</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6079</v>
+        <v>0.5269</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0384</v>
+        <v>-0.1841</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4523</v>
+        <v>1.9295</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1692</v>
+        <v>1.7222</v>
       </c>
       <c r="F4" t="n">
-        <v>1.283</v>
+        <v>0.2073</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9765</v>
+        <v>2.5685</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2167</v>
+        <v>2.9615</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7598</v>
+        <v>-0.393</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1945</v>
+        <v>1.9481</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0452</v>
+        <v>2.5888</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.782</v>
+        <v>0.6204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1715</v>
+        <v>0.3727</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1563</v>
+        <v>0.2927</v>
       </c>
       <c r="T4" t="n">
-        <v>2.468</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6883</v>
+        <v>-0.4618</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2249</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0249</v>
+        <v>0.9131</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0316</v>
+        <v>-0.2154</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0067</v>
+        <v>1.1285</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5685</v>
+        <v>1.9677</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9683</v>
+        <v>1.1986</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3998</v>
+        <v>0.7691</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9706</v>
+        <v>1.1617</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6077</v>
+        <v>1.0128</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6371</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5979</v>
+        <v>0.806</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3605</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2373</v>
+        <v>0.6201</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3883</v>
+        <v>1.6283</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0344</v>
+        <v>1.1284</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.646</v>
+        <v>0.4999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>-0.2292</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4481</v>
+        <v>0.8454</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1542</v>
+        <v>-0.1001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.9454</v>
       </c>
       <c r="G6" t="n">
-        <v>1.256</v>
+        <v>1.2685</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1141</v>
+        <v>-0.1067</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3701</v>
+        <v>1.3751</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0631</v>
+        <v>0.0493</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7375</v>
+        <v>0.7272</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1929</v>
+        <v>1.2192</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O6" t="n">
-        <v>2.0445</v>
+        <v>2.0531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7833</v>
+        <v>-0.4019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.378</v>
+        <v>-0.3071</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4053</v>
+        <v>-0.0948</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6805</v>
+        <v>-0.4734</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4515</v>
+        <v>0.0735</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2291</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3362</v>
+        <v>1.8064</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.2762</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4718</v>
+        <v>2.0826</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.769</v>
+        <v>1.3467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.1551</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7864</v>
+        <v>1.1916</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5672</v>
+        <v>0.4597</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8817</v>
+        <v>-0.4314</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3145</v>
+        <v>0.8911</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4289</v>
+        <v>-0.3496</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3176</v>
+        <v>-0.135</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1113</v>
+        <v>-0.2146</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7824</v>
+        <v>-0.5481</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1086</v>
+        <v>-1.1001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3262</v>
+        <v>0.5521</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7332</v>
+        <v>1.7146</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2206</v>
+        <v>-0.232</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9538</v>
+        <v>1.9466</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4334</v>
+        <v>0.378</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0337</v>
+        <v>-0.001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3997</v>
+        <v>0.3789</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2998</v>
+        <v>1.3366</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5541</v>
+        <v>1.5677</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4494</v>
+        <v>-0.1928</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5656</v>
+        <v>0.6405</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.015</v>
+        <v>-0.8333</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0281</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1791</v>
+        <v>0.2913</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2072</v>
+        <v>-1.1687</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1828</v>
+        <v>0.1807</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3449</v>
+        <v>-0.3419</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5226</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3878</v>
+        <v>0.3819</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3451</v>
+        <v>-0.1963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0549</v>
+        <v>-0.8963</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3921</v>
+        <v>-0.7378</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.1585</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7933</v>
+        <v>-1.3328</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2859</v>
+        <v>-0.859</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0791</v>
+        <v>-0.4738</v>
       </c>
       <c r="J10" t="n">
-        <v>1.35</v>
+        <v>-0.7724</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1559</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1941</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4433</v>
+        <v>-0.5604</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4417</v>
+        <v>-0.8763</v>
       </c>
       <c r="O10" t="n">
-        <v>0.885</v>
+        <v>0.3159</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9143</v>
+        <v>0.2089</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6079</v>
+        <v>0.0346</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3064</v>
+        <v>0.1743</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1921</v>
+        <v>-2.2566</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0127</v>
+        <v>-0.5752</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1794</v>
+        <v>-1.6814</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1443</v>
+        <v>-0.1526</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0156</v>
+        <v>-2.0298</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8712</v>
+        <v>1.8772</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.524</v>
+        <v>-0.5545</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1957</v>
+        <v>-1.2248</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3797</v>
+        <v>0.4019</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6554</v>
+        <v>-0.3984</v>
       </c>
       <c r="T11" t="n">
-        <v>0.617</v>
+        <v>0.0994</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0384</v>
+        <v>-0.4978</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0527</v>
+        <v>-4.2938</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1525</v>
+        <v>-4.3431</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0999</v>
+        <v>0.0493</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1138</v>
+        <v>-4.1259</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4748</v>
+        <v>-1.4707</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.639</v>
+        <v>-2.6552</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.4721</v>
+        <v>-3.4946</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7377</v>
+        <v>-2.7566</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6417</v>
+        <v>-0.6314</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1518</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>-0.0746</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0611</v>
+        <v>-0.0022</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.508800000000001</v>
+        <v>4.192900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9093</v>
+        <v>1.3203</v>
       </c>
       <c r="F13" t="n">
-        <v>2.599399999999999</v>
+        <v>2.8728</v>
       </c>
       <c r="G13" t="n">
-        <v>11.42</v>
+        <v>11.4019</v>
       </c>
       <c r="H13" t="n">
-        <v>3.463299999999999</v>
+        <v>3.4475</v>
       </c>
       <c r="I13" t="n">
-        <v>7.956500000000002</v>
+        <v>7.954399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.611599999999997</v>
+        <v>5.362299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.705100000000001</v>
+        <v>6.542900000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0936</v>
+        <v>-1.1806</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8084</v>
+        <v>6.0396</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.2417</v>
+        <v>-3.0955</v>
       </c>
       <c r="O13" t="n">
-        <v>9.049999999999999</v>
+        <v>9.135200000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-0.0001000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105400000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09069999999999973</v>
+        <v>0.7896</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0568</v>
+        <v>2.7831</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.966</v>
+        <v>-1.9935</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.0021</v>
+        <v>-7.9984</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3143</v>
+        <v>2.2803</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.3164</v>
+        <v>-10.2787</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4923</v>
+        <v>4.0577</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4973</v>
+        <v>3.5364</v>
       </c>
       <c r="F14" t="n">
-        <v>0.995</v>
+        <v>0.5213</v>
       </c>
       <c r="G14" t="n">
-        <v>3.099</v>
+        <v>3.0981</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3926</v>
+        <v>2.3843</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7064</v>
+        <v>0.7139</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0606</v>
+        <v>3.0397</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0233</v>
+        <v>3.0025</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0383</v>
+        <v>0.0584</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8735</v>
+        <v>1.4344</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6635</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>0.7101</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9283</v>
+        <v>2.0594</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4413</v>
+        <v>1.2124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.487</v>
+        <v>0.847</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8279</v>
+        <v>-3.8373</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4761</v>
+        <v>-3.0849</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3519</v>
+        <v>-0.7524</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6088</v>
+        <v>-4.0974</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5715</v>
+        <v>-2.8828</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>-1.2146</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2192</v>
+        <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0954</v>
+        <v>-0.2022</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3145</v>
+        <v>0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6902</v>
+        <v>0.7469</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8741</v>
+        <v>0.8428</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1839</v>
+        <v>-0.0959</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3176</v>
+        <v>5.6051</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>5.6051</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9661</v>
+        <v>1.7097</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8267</v>
+        <v>1.1456</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8606</v>
+        <v>0.5641</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7569</v>
+        <v>-0.4123</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1141</v>
+        <v>1.2993</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3572</v>
+        <v>-1.7116</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1367</v>
+        <v>-0.3709</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7289</v>
+        <v>1.9608</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4078</v>
+        <v>-2.3317</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3798</v>
+        <v>-0.0414</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6149</v>
+        <v>-0.6615</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7649</v>
+        <v>0.6201</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2604</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5293</v>
+        <v>0.6546</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2689</v>
+        <v>0.1503</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.944</v>
+        <v>1.6361</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7202</v>
+        <v>1.1983</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2239</v>
+        <v>0.4377</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3921</v>
+        <v>0.8353</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3192</v>
+        <v>0.4822</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7113</v>
+        <v>0.3531</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3241</v>
+        <v>0.6061</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9976</v>
+        <v>0.5688</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3218</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.068</v>
+        <v>0.2292</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6785</v>
+        <v>-0.0866</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6105</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0166</v>
+        <v>0.3926</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1785</v>
+        <v>0.641</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1618</v>
+        <v>-0.2483</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.3187</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9212</v>
+        <v>0.2702</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6673</v>
+        <v>2.9738</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2539</v>
+        <v>-2.7035</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8399</v>
+        <v>1.7513</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.0909</v>
+        <v>2.1057</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.749</v>
+        <v>-0.3544</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.0706</v>
+        <v>3.1114</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.8684</v>
+        <v>2.7094</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2023</v>
+        <v>0.4019</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2307</v>
+        <v>-1.3601</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2225</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4092</v>
+        <v>-0.4403</v>
       </c>
       <c r="T18" t="n">
-        <v>0.248</v>
+        <v>-0.2954</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6572</v>
+        <v>-0.1449</v>
       </c>
       <c r="V18" t="n">
-        <v>5.6241</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>5.6241</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3608</v>
+        <v>0.1642</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7491</v>
+        <v>-1.3456</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1099</v>
+        <v>1.5098</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6211</v>
+        <v>-1.6099</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5412</v>
+        <v>-1.5341</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0799</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1313</v>
+        <v>-2.1421</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3822</v>
+        <v>-1.3897</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5102</v>
+        <v>0.5322</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.757</v>
+        <v>0.5448</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3822</v>
+        <v>0.7965</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6252</v>
+        <v>-0.2516</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6555</v>
+        <v>-0.6837</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5996</v>
+        <v>-0.1579</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0558</v>
+        <v>-0.5258</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6419</v>
+        <v>1.6447</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0288</v>
+        <v>1.031</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6131</v>
+        <v>0.6138</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7121</v>
+        <v>2.6902</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7073</v>
+        <v>1.6925</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0702</v>
+        <v>-1.0455</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2293</v>
+        <v>-1.2601</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0434</v>
+        <v>-0.5718</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1859</v>
+        <v>-0.6884</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1802</v>
+        <v>-2.302</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.133</v>
+        <v>-2.0829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9528</v>
+        <v>-0.2191</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0837</v>
+        <v>-2.4134</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2943</v>
+        <v>-0.4887</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2106</v>
+        <v>-1.9247</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4535</v>
+        <v>-1.0954</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1123</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3413</v>
+        <v>-1.6987</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6302</v>
+        <v>-1.318</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1821</v>
+        <v>-1.092</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.226</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0526</v>
+        <v>-0.7991</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3962</v>
+        <v>-0.7599</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4488</v>
+        <v>-0.0392</v>
       </c>
       <c r="V21" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7565</v>
+        <v>-2.318</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4211</v>
+        <v>-3.179</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3354</v>
+        <v>0.861</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4184</v>
+        <v>-2.0789</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4965</v>
+        <v>-2.292</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9219</v>
+        <v>0.2131</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0813</v>
+        <v>-1.4783</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6061</v>
+        <v>-1.1279</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6874</v>
+        <v>-0.3505</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3371</v>
+        <v>-0.6006</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1026</v>
+        <v>-1.1642</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2345</v>
+        <v>0.5636</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2455</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>-0.3953</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1325</v>
+        <v>0.3234</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5568</v>
+        <v>-2.8996</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6421</v>
+        <v>-2.3038</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9147</v>
+        <v>-0.5958</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3733</v>
+        <v>-3.362</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3644</v>
+        <v>-2.3702</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7408</v>
+        <v>-1.7574</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6325</v>
+        <v>-1.6047</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9962</v>
+        <v>-0.3602</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6744</v>
+        <v>-0.3188</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3218</v>
+        <v>-0.0414</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9726</v>
+        <v>-3.6105</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2074</v>
+        <v>-3.8699</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2348</v>
+        <v>0.2594</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.0171</v>
+        <v>-5.0173</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3622</v>
+        <v>-2.3582</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6549</v>
+        <v>-2.6592</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.525</v>
+        <v>-4.5455</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2032</v>
+        <v>-2.2138</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4921</v>
+        <v>-0.4719</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1391</v>
+        <v>0.4947</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3176</v>
+        <v>0.6756</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1785</v>
+        <v>-0.1808</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5089</v>
+        <v>-1.9165</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5995</v>
+        <v>-2.872599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9091999999999997</v>
+        <v>0.9560999999999997</v>
       </c>
       <c r="G25" t="n">
-        <v>-11.4199</v>
+        <v>-11.4017</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.463199999999999</v>
+        <v>-3.4472</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.9566</v>
+        <v>-7.954400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.808400000000002</v>
+        <v>-6.0396</v>
       </c>
       <c r="K25" t="n">
-        <v>3.241799999999998</v>
+        <v>3.0955</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.0504</v>
+        <v>-9.135400000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.611499999999999</v>
+        <v>-5.3624</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.705399999999999</v>
+        <v>-6.5429</v>
       </c>
       <c r="O25" t="n">
-        <v>1.0936</v>
+        <v>1.180699999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0.0001000000000003221</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.073200000000002</v>
+        <v>-9.105200000000002</v>
       </c>
       <c r="R25" t="n">
-        <v>9.073500000000001</v>
+        <v>9.105499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.09079999999999999</v>
+        <v>1.486699999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9662</v>
+        <v>1.9936</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0569</v>
+        <v>-0.5066999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>8.002100000000002</v>
+        <v>7.998399999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>10.3163</v>
+        <v>10.2786</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.3143</v>
+        <v>-2.2802</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104561_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104561_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.2787</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104561_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-2.2802</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
